--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -759,7 +759,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>山顶道77D号</t>
+          <t>山顶道77C号</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6266</v>
+        <v>6257</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -787,14 +787,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>551408000</v>
+        <v>500560000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>88000</v>
+        <v>80000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>山顶道77E号</t>
+          <t>山顶道77D号</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7527</v>
+        <v>6266</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-03-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>677430000</v>
+        <v>551408000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>90000</v>
+        <v>88000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>山顶道77F号</t>
+          <t>山顶道77E号</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6061</v>
+        <v>7527</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -879,14 +879,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>558145368</v>
+        <v>677430000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>92088</v>
+        <v>90000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>山顶道79号</t>
+          <t>山顶道77F号</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8139</v>
+        <v>6061</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -925,14 +925,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>481000000</v>
+        <v>558145368</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>59098</v>
+        <v>92088</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -943,44 +943,90 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>山顶道79号</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>8139</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2018-11-20</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>481000000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>59098</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>山顶道79A号</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>7896</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>2018-11-20</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>479000000</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>60664</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1001,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,6 +1058,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1056,7 +1103,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1071,7 +1118,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1103,25 +1150,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>山顶道77C号</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>山顶道77D号</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>山顶道77E号</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>山顶道77F号</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>山顶道79A号</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>山顶道79号</t>
         </is>
@@ -1153,6 +1205,15 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
+          <t>山顶道77C号
+6257呎 (4+房)
+(25年-01月)
+$5.01亿
+$80,000/呎</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
           <t>山顶道77D号
 6266呎 (4+房)
 (21年-03月)
@@ -1160,7 +1221,7 @@
 $88,000/呎</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>山顶道77E号
 7527呎 (4+房)
@@ -1169,7 +1230,7 @@
 $90,000/呎</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>山顶道77F号
 6061呎 (4+房)
@@ -1178,7 +1239,7 @@
 $92,088/呎</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
@@ -1187,7 +1248,7 @@
 $60,664/呎</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>山顶道79号
 8139呎 (4+房)
@@ -1199,7 +1260,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -178,49 +178,49 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -603,6 +603,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -660,6 +664,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -695,7 +719,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -705,6 +729,26 @@
         <v>80942</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -741,7 +785,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -751,6 +795,26 @@
         <v>90006</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -787,7 +851,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -797,6 +861,26 @@
         <v>80000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -833,7 +917,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -843,6 +927,26 @@
         <v>88000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -879,7 +983,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -889,6 +993,26 @@
         <v>90000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -925,7 +1049,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -935,6 +1059,26 @@
         <v>92088</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -971,7 +1115,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -981,6 +1125,26 @@
         <v>59098</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1017,7 +1181,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1027,6 +1191,26 @@
         <v>60664</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1034,7 +1218,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1189,7 +1373,7 @@
         <is>
           <t>山顶道77A号
 7388呎 (4+房)
-(21年-03月)
+(21年-03月-11日)
 $5.98亿
 $80,942/呎</t>
         </is>
@@ -1198,7 +1382,7 @@
         <is>
           <t>山顶道77B号
 6676呎 (4+房)
-(21年-04月)
+(21年-04月-14日)
 $6.01亿
 $90,006/呎</t>
         </is>
@@ -1207,7 +1391,7 @@
         <is>
           <t>山顶道77C号
 6257呎 (4+房)
-(25年-01月)
+(25年-01月-17日)
 $5.01亿
 $80,000/呎</t>
         </is>
@@ -1216,7 +1400,7 @@
         <is>
           <t>山顶道77D号
 6266呎 (4+房)
-(21年-03月)
+(21年-03月-15日)
 $5.51亿
 $88,000/呎</t>
         </is>
@@ -1225,7 +1409,7 @@
         <is>
           <t>山顶道77E号
 7527呎 (4+房)
-(21年-04月)
+(21年-04月-08日)
 $6.77亿
 $90,000/呎</t>
         </is>
@@ -1234,7 +1418,7 @@
         <is>
           <t>山顶道77F号
 6061呎 (4+房)
-(21年-03月)
+(21年-03月-18日)
 $5.58亿
 $92,088/呎</t>
         </is>
@@ -1243,7 +1427,7 @@
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
-(18年-11月)
+(18年-11月-21日)
 $4.79亿
 $60,664/呎</t>
         </is>
@@ -1252,7 +1436,7 @@
         <is>
           <t>山顶道79号
 8139呎 (4+房)
-(18年-11月)
+(18年-11月-21日)
 $4.81亿
 $59,098/呎</t>
         </is>

--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -178,49 +178,49 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -603,10 +603,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -664,26 +660,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -719,7 +695,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -730,26 +706,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -785,7 +741,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -796,26 +752,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -851,7 +787,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -862,26 +798,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -917,7 +833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -928,26 +844,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -955,7 +851,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>山顶道77E号</t>
+          <t>山顶道77F号</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -974,7 +870,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7527</v>
+        <v>6061</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -983,36 +879,16 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>677430000</v>
+        <v>558145368</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>90000</v>
+        <v>92088</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1021,7 +897,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>山顶道77F号</t>
+          <t>山顶道79号</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1040,7 +916,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6061</v>
+        <v>8139</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1049,36 +925,16 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>558145368</v>
+        <v>481000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>92088</v>
+        <v>59098</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1087,7 +943,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>山顶道79号</t>
+          <t>山顶道79A号</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1106,7 +962,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8139</v>
+        <v>7896</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1115,102 +971,16 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-11-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>481000000</v>
+        <v>479000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>59098</v>
+        <v>60664</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>山顶道79A号</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>7896</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-21</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>479000000</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>60664</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1218,7 +988,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1231,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1242,7 +1012,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1287,7 +1056,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1302,7 +1071,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1344,20 +1113,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>山顶道77E号</t>
+          <t>山顶道77F号</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>山顶道77F号</t>
+          <t>山顶道79A号</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>山顶道79A号</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>山顶道79号</t>
         </is>
@@ -1373,7 +1137,7 @@
         <is>
           <t>山顶道77A号
 7388呎 (4+房)
-(21年-03月-11日)
+(21年-03月-10日)
 $5.98亿
 $80,942/呎</t>
         </is>
@@ -1382,7 +1146,7 @@
         <is>
           <t>山顶道77B号
 6676呎 (4+房)
-(21年-04月-14日)
+(21年-04月-13日)
 $6.01亿
 $90,006/呎</t>
         </is>
@@ -1391,7 +1155,7 @@
         <is>
           <t>山顶道77C号
 6257呎 (4+房)
-(25年-01月-17日)
+(25年-01月-16日)
 $5.01亿
 $80,000/呎</t>
         </is>
@@ -1400,43 +1164,34 @@
         <is>
           <t>山顶道77D号
 6266呎 (4+房)
-(21年-03月-15日)
+(21年-03月-14日)
 $5.51亿
 $88,000/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>山顶道77E号
-7527呎 (4+房)
-(21年-04月-08日)
-$6.77亿
-$90,000/呎</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
           <t>山顶道77F号
 6061呎 (4+房)
-(21年-03月-18日)
+(21年-03月-17日)
 $5.58亿
 $92,088/呎</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
-(18年-11月-21日)
+(18年-11月-20日)
 $4.79亿
 $60,664/呎</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>山顶道79号
 8139呎 (4+房)
-(18年-11月-21日)
+(18年-11月-20日)
 $4.81亿
 $59,098/呎</t>
         </is>
@@ -1444,7 +1199,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -178,49 +178,49 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -603,6 +603,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -660,6 +664,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -695,7 +719,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -705,6 +729,26 @@
         <v>80942</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -741,7 +785,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -751,6 +795,26 @@
         <v>90006</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -787,7 +851,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -797,6 +861,26 @@
         <v>80000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -833,7 +917,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -843,6 +927,26 @@
         <v>88000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -851,7 +955,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>山顶道77F号</t>
+          <t>山顶道77E号</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -870,7 +974,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6061</v>
+        <v>7527</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -879,16 +983,36 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>558145368</v>
+        <v>677430000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>92088</v>
+        <v>90000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -897,7 +1021,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>山顶道79号</t>
+          <t>山顶道77F号</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -916,7 +1040,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8139</v>
+        <v>6061</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -925,16 +1049,36 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>481000000</v>
+        <v>558145368</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>59098</v>
+        <v>92088</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -943,44 +1087,130 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>山顶道79号</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>8139</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2018-11-21</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>481000000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>59098</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>山顶道79A号</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>7896</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2018-11-20</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2018-11-21</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>479000000</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>60664</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -988,7 +1218,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1001,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,6 +1242,7 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1056,7 +1287,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1071,7 +1302,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1113,15 +1344,20 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>山顶道77E号</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>山顶道77F号</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>山顶道79A号</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>山顶道79号</t>
         </is>
@@ -1137,7 +1373,7 @@
         <is>
           <t>山顶道77A号
 7388呎 (4+房)
-(21年-03月-10日)
+(21年-03月-11日)
 $5.98亿
 $80,942/呎</t>
         </is>
@@ -1146,7 +1382,7 @@
         <is>
           <t>山顶道77B号
 6676呎 (4+房)
-(21年-04月-13日)
+(21年-04月-14日)
 $6.01亿
 $90,006/呎</t>
         </is>
@@ -1155,7 +1391,7 @@
         <is>
           <t>山顶道77C号
 6257呎 (4+房)
-(25年-01月-16日)
+(25年-01月-17日)
 $5.01亿
 $80,000/呎</t>
         </is>
@@ -1164,34 +1400,43 @@
         <is>
           <t>山顶道77D号
 6266呎 (4+房)
-(21年-03月-14日)
+(21年-03月-15日)
 $5.51亿
 $88,000/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
+          <t>山顶道77E号
+7527呎 (4+房)
+(21年-04月-08日)
+$6.77亿
+$90,000/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
           <t>山顶道77F号
 6061呎 (4+房)
-(21年-03月-17日)
+(21年-03月-18日)
 $5.58亿
 $92,088/呎</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
-(18年-11月-20日)
+(18年-11月-21日)
 $4.79亿
 $60,664/呎</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>山顶道79号
 8139呎 (4+房)
-(18年-11月-20日)
+(18年-11月-21日)
 $4.81亿
 $59,098/呎</t>
         </is>
@@ -1199,7 +1444,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -178,49 +178,49 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -603,10 +603,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -664,26 +660,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -719,7 +695,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -730,26 +706,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -785,7 +741,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -796,26 +752,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -851,7 +787,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -862,26 +798,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -917,7 +833,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-03-15</t>
+          <t>2021-03-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -928,26 +844,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -983,7 +879,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -994,26 +890,6 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1049,7 +925,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1060,26 +936,6 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1115,7 +971,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-11-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1126,26 +982,6 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1181,7 +1017,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-11-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1192,33 +1028,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1373,7 +1189,7 @@
         <is>
           <t>山顶道77A号
 7388呎 (4+房)
-(21年-03月-11日)
+(21年-03月-10日)
 $5.98亿
 $80,942/呎</t>
         </is>
@@ -1382,7 +1198,7 @@
         <is>
           <t>山顶道77B号
 6676呎 (4+房)
-(21年-04月-14日)
+(21年-04月-13日)
 $6.01亿
 $90,006/呎</t>
         </is>
@@ -1391,7 +1207,7 @@
         <is>
           <t>山顶道77C号
 6257呎 (4+房)
-(25年-01月-17日)
+(25年-01月-16日)
 $5.01亿
 $80,000/呎</t>
         </is>
@@ -1400,7 +1216,7 @@
         <is>
           <t>山顶道77D号
 6266呎 (4+房)
-(21年-03月-15日)
+(21年-03月-14日)
 $5.51亿
 $88,000/呎</t>
         </is>
@@ -1409,7 +1225,7 @@
         <is>
           <t>山顶道77E号
 7527呎 (4+房)
-(21年-04月-08日)
+(21年-04月-07日)
 $6.77亿
 $90,000/呎</t>
         </is>
@@ -1418,7 +1234,7 @@
         <is>
           <t>山顶道77F号
 6061呎 (4+房)
-(21年-03月-18日)
+(21年-03月-17日)
 $5.58亿
 $92,088/呎</t>
         </is>
@@ -1427,7 +1243,7 @@
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
-(18年-11月-21日)
+(18年-11月-20日)
 $4.79亿
 $60,664/呎</t>
         </is>
@@ -1436,7 +1252,7 @@
         <is>
           <t>山顶道79号
 8139呎 (4+房)
-(18年-11月-21日)
+(18年-11月-20日)
 $4.81亿
 $59,098/呎</t>
         </is>

--- a/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
+++ b/港岛-山顶区-7779 Peak Road/7779 Peak Road_销控明细表.xlsx
@@ -178,49 +178,49 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -603,6 +603,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -660,6 +664,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -695,7 +719,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -705,6 +729,26 @@
         <v>80942</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -741,7 +785,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-04-13</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -751,6 +795,26 @@
         <v>90006</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -787,7 +851,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -797,6 +861,26 @@
         <v>80000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -833,7 +917,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-03-14</t>
+          <t>2021-03-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -843,6 +927,26 @@
         <v>88000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -879,7 +983,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -889,6 +993,26 @@
         <v>90000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -925,7 +1049,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -935,6 +1059,26 @@
         <v>92088</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -971,7 +1115,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -981,6 +1125,26 @@
         <v>59098</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1017,7 +1181,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1027,6 +1191,26 @@
         <v>60664</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1034,7 +1218,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1189,7 +1373,7 @@
         <is>
           <t>山顶道77A号
 7388呎 (4+房)
-(21年-03月-10日)
+(21年-03月-11日)
 $5.98亿
 $80,942/呎</t>
         </is>
@@ -1198,7 +1382,7 @@
         <is>
           <t>山顶道77B号
 6676呎 (4+房)
-(21年-04月-13日)
+(21年-04月-14日)
 $6.01亿
 $90,006/呎</t>
         </is>
@@ -1207,7 +1391,7 @@
         <is>
           <t>山顶道77C号
 6257呎 (4+房)
-(25年-01月-16日)
+(25年-01月-17日)
 $5.01亿
 $80,000/呎</t>
         </is>
@@ -1216,7 +1400,7 @@
         <is>
           <t>山顶道77D号
 6266呎 (4+房)
-(21年-03月-14日)
+(21年-03月-15日)
 $5.51亿
 $88,000/呎</t>
         </is>
@@ -1225,7 +1409,7 @@
         <is>
           <t>山顶道77E号
 7527呎 (4+房)
-(21年-04月-07日)
+(21年-04月-08日)
 $6.77亿
 $90,000/呎</t>
         </is>
@@ -1234,7 +1418,7 @@
         <is>
           <t>山顶道77F号
 6061呎 (4+房)
-(21年-03月-17日)
+(21年-03月-18日)
 $5.58亿
 $92,088/呎</t>
         </is>
@@ -1243,7 +1427,7 @@
         <is>
           <t>山顶道79A号
 7896呎 (4+房)
-(18年-11月-20日)
+(18年-11月-21日)
 $4.79亿
 $60,664/呎</t>
         </is>
@@ -1252,7 +1436,7 @@
         <is>
           <t>山顶道79号
 8139呎 (4+房)
-(18年-11月-20日)
+(18年-11月-21日)
 $4.81亿
 $59,098/呎</t>
         </is>
